--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,7 +503,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Engineer- Technology</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,15 +513,15 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,24 +531,24 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34bd7ad3cc55cc</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer- Technology</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,14 +636,14 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,42 +836,42 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer III Java/ PySpark/AWS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,137 +951,137 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior PS Sales Solutions Architect</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8380914e78d30a86</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,94 +1091,94 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tango Technology, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Backend (Java)</t>
+          <t>Full Stack Web Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Revstar</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2213405e0bc35e97</t>
+          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Developer / Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior AWS Cloud Developer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=9def542b10d50c48</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,19 +1931,19 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Python Full Stack Developer with Agentic AI</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>System Edge LLC.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
@@ -2183,25 +2183,25 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Python Full Stack Developer with Agentic AI</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>System Edge LLC.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>RDS, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,15 +2753,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,67 +2771,67 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2862,11 +2862,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=e77d95b867714292</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e77d95b867714292</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Aires</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb4e9cb29fe1df7</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=211199e7b69b9eed</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aires</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb4e9cb29fe1df7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7b93f1801a596bf</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Senior Backend Engineer - MoneyLion</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, SQS, API Gateway, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=a5243fde3ff4e011</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IT Data Platform Data Engineer (2 Openings)</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>PNM</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b8dc4289e41437b</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - MoneyLion</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5243fde3ff4e011</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Lancer Worldwide</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Scala, Data Modeling, ELT, Power BI, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=700578b94883b043</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Waitsfield, VT, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Architect AI ML</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Nightingale College</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Platform Architect - FinOps experience is Mandatory</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,17 +4196,122 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Platform Architect - FinOps experience is Mandatory</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>VTekis Consulting LLP</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Plainsboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Lancer Worldwide</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Synapse Analytics, Scala, Data Modeling, ELT, Power BI, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=700578b94883b043</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G111"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Computing Architect (Mid-Level or Senior)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Boeing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=38348253fb6b3f9a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,17 +836,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
@@ -958,52 +958,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>Senior AWS Engineer - ML</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,139 +1151,139 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tango Technology, Inc.</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9226866e941cd9b2</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Software Engineer III - Machine Learning Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f7d7f71cdcf553a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Azure Data &amp; Microsoft Fabric Engineer</t>
+          <t>Senior Data Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Dataflow, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,19 +1476,19 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93d133881ebcebcf</t>
+          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=934468e669a4c3eb</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Software Engineer III- Python/PySpark</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b3b92c71d4ed281</t>
+          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Full Stack Web Developer</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Revstar</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, API Gateway, ECS, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e87bd4ec5626fc3</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Senior AWS Cloud Developer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Westlake, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=9def542b10d50c48</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Senior Business Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=3188efd79bf1e92f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c2ecce1ec4e1cba</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Developer / Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Impala</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc02f3b1065e1623</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9def542b10d50c48</t>
+          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,24 +2061,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Big Data Developer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>M.P. Excavation LLC</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af8b65d1f85bb1e9</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Python Full Stack Developer with Agentic AI</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>System Edge LLC.</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Python Full Stack Developer with Agentic AI</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>System Edge LLC.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>RDS, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Tableau/Python Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>RCR Technology</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=872667539c482fb1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,14 +2876,14 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2893,15 +2893,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Senior AI Full Stack Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Panasonic Automotive</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e77d95b867714292</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>Python Engineer, Senior Associate</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Software Engineer III- AWS/Python/PySpark</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Vertex AI, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f4ef0ab2b33f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211199e7b69b9eed</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Aires</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb4e9cb29fe1df7</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Backend Architect - Device Management Platforms</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=143762682a9d9c04</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Altom Transport, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=e77d95b867714292</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Sr Adv Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Resideo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=2949635dab79e305</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Aires</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cb4e9cb29fe1df7</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JLL</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=211199e7b69b9eed</t>
         </is>
       </c>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - MoneyLion</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5243fde3ff4e011</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Waitsfield, VT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Senior Backend Engineer - MoneyLion</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, SQS, API Gateway, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=a5243fde3ff4e011</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Sr. QE (Senior Quality Engineer, APIs)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, Azure, DynamoDB, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+          <t>https://www.indeed.com/viewjob?jk=c4837acc95c44131</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. QE (Senior Quality Engineer, APIs)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nightingale College</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, Azure, DynamoDB, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+          <t>https://www.indeed.com/viewjob?jk=5641d051b78dc3e5</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Platform Architect - FinOps experience is Mandatory</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Lancer Worldwide</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,15 +4301,260 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Engineer II</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Engineer II- .Net</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Nightingale College</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>IS Technical Specialist</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Huntington Bank</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Platform Architect - FinOps experience is Mandatory</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>VTekis Consulting LLP</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Plainsboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Data Analyst</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Lancer Worldwide</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>San Antonio, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Synapse Analytics, Scala, Data Modeling, ELT, Power BI, CI/CD, Python</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=700578b94883b043</t>
         </is>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Computing Architect (Mid-Level or Senior)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boeing</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Azure, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38348253fb6b3f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,14 +671,14 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Software Engineer III - Big Data Pyspark, Java And AWS</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42a4d9b7a78ea546</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,29 +871,29 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -902,11 +902,11 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III Java/ PySpark/AWS</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ef67511e4c2316e</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
+          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,94 +1021,94 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior AWS Engineer - ML</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Step Functions, ECS, RDS, Scala, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f410f9011272b97</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,42 +1116,42 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,137 +1161,137 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - Machine Learning Platform</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, MLOps, CI/CD</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcccef4ffd260d2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Software Engineer</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Step Functions, ECS, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,102 +1476,102 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24e84f8f2d7fe85a</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Engineer III- Python/PySpark</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Databricks, Spark, PySpark, Scala, PostgreSQL</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e02e62d3136c61c7</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,129 +1651,129 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Developer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Westlake, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9def542b10d50c48</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Business Data Analyst</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3188efd79bf1e92f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer III - Fullstack, Python, AWS, AI/ML</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, GCP, Scala, Splunk</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f053e3efceefd1</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Python Full Stack Developer with Agentic AI</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>System Edge LLC.</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,19 +2701,19 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Tableau/Python Developer</t>
+          <t>AI Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RCR Technology</t>
+          <t>CloudGeometry</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Scala, Snowflake, Oracle, SQL Server, Data Modeling, Tableau</t>
+          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=872667539c482fb1</t>
+          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Township of Hamilton, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,49 +2911,49 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior AI Full Stack Engineer</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Panasonic Automotive</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Kafka, PostgreSQL, MongoDB, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e634c843fef9248e</t>
+          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Sr. Palantir Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,15 +2963,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Python Engineer, Senior Associate</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Polars, PostgreSQL, CI/CD, Jenkins, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b88929d02f381224</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer III- AWS/Python/PySpark</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623b2a2f5c4be4df</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,15 +3278,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Backend Architect - Device Management Platforms</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143762682a9d9c04</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Engineer (Cloud, Cross-Platform &amp; .NET Systems)</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Altom Transport, Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Scala, SQL Server, MySQL, CI/CD, Jenkins, GitHub Actions, Docker, Jenkins, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e77d95b867714292</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr Adv Software Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Resideo</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Azure, Scala, Kafka, SQL Server, MongoDB, DynamoDB</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2949635dab79e305</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Aires</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, DynamoDB, CI/CD, Docker, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cb4e9cb29fe1df7</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>JLL</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=211199e7b69b9eed</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Health Data Analytics Institute</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Dedham, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,137 +3576,137 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Software Engineer - Python - AI Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, GCP, Vertex AI, Scala, Kafka, Data Modeling, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=a91ebd3753be4d7e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=19bc2fde31ea0812</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Platform Architect - FinOps experience is Mandatory</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>VTekis Consulting LLP</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plainsboro, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,532 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Health Data Analytics Institute</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Dedham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Senior Backend Engineer - MoneyLion</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Gen Digital Inc.</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, SQS, API Gateway, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5243fde3ff4e011</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sr. QE (Senior Quality Engineer, APIs)</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Subway</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Shelton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, Azure, DynamoDB, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4837acc95c44131</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Sr. QE (Senior Quality Engineer, APIs)</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Subway</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Shelton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, Azure, DynamoDB, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5641d051b78dc3e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Architect AI ML</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>3Pillar Global</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Waitsfield, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>IT Developer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>First Horizon Bank</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Nightingale College</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Platform Architect - FinOps experience is Mandatory</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>VTekis Consulting LLP</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Plainsboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Lancer Worldwide</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Scala, Data Modeling, ELT, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=700578b94883b043</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G103"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Data Engineer (SQL, Python, Cloud)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34bd7ad3cc55cc</t>
+          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer- Technology</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34bd7ad3cc55cc</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer- Technology</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,69 +871,69 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>Java Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
+          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Datalink Networks Inc.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Valencia, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,42 +1126,42 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
@@ -1273,25 +1273,25 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Oracle NetSuite Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,77 +1476,77 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
         </is>
       </c>
     </row>
@@ -1658,17 +1658,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
@@ -1826,14 +1826,14 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,42 +2061,42 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>AI Developer</t>
+          <t>Java/.NET Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CloudGeometry</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, MySQL, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=494b669d4a90f93c</t>
+          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,15 +2753,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
@@ -2988,17 +2988,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Solutions Engineer II - Networking</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
+          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
         </is>
       </c>
     </row>
@@ -3583,17 +3583,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Python - AI Platform</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HEB</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,17 +3601,17 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, GCP, Vertex AI, Scala, Kafka, Data Modeling, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a91ebd3753be4d7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
@@ -3653,17 +3653,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Software Engineer - Python - AI Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>RDS, GCP, Vertex AI, Scala, Kafka, Data Modeling, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+          <t>https://www.indeed.com/viewjob?jk=a91ebd3753be4d7e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Waitsfield, VT, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,14 +3786,14 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
+          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Engineer II</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,14 +3856,14 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
+          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Engineer II- .Net</t>
+          <t>Engineer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
+          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Architect AI ML</t>
+          <t>Engineer II- .Net</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nightingale College</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Platform Architect - FinOps experience is Mandatory</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>VTekis Consulting LLP</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Plainsboro, NJ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,15 +4021,50 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Platform Architect - FinOps experience is Mandatory</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>VTekis Consulting LLP</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Plainsboro, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
         </is>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Engineer- Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka, Oracle</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5b12becd9332b9d</t>
+          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,77 +871,77 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Java Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, GCP, Scala, Kafka, Oracle, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293b45603c9830da</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Datalink Networks Inc.</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Valencia, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,139 +1046,139 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, BigQuery, Spark, Scala, Snowflake, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fa2a7970470f14c</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Oracle NetSuite Data Engineer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Glue, EMR, Redshift, S3, RDS, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c132bd645a73aa20</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>DevOps &amp; MLOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>TailoredSearch</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,102 +1406,102 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580d44c93ad196b2</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ed2aa63753dfb4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,24 +1956,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Senior Python Full Stack Developer with Agentic AI</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>System Edge LLC.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>RDS, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,59 +2106,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>Gen AI Platform &amp; Deployment Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>GeoStabilization International</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Westminster, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>BOK Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Summer Intern - Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, PostgreSQL, MySQL, Cassandra, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af03499a4d1674ae</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,67 +2666,67 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Java/.NET Developer</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88378f15de50673d</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>Senior Backend Architect - Device Management Platforms</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Elevance Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=143762682a9d9c04</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Township of Hamilton, NJ, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, SQL Server, ETL, ELT, Power BI, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4e10db55253ba6</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794267568ebf50df</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr. Palantir Developer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, PySpark, Scala, Data Modeling, CI/CD, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,67 +2981,67 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af5152de96557363</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Medallion Architecture, Hadoop, Spark, PySpark, Scala, Kafka, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ddcdc29f72dd2b8</t>
+          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0c9eac7df91cbba</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0313297f092b51b7</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0d7013f328ba7a</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Solutions Engineer II - Networking</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5a8d63272e83315</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Senior Backend Engineer - MoneyLion</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Gen Digital Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, SQS, API Gateway, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,59 +3226,59 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=a5243fde3ff4e011</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Clinical Data Scientist, Human Capital</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>CHS Corporate</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=bfe6028a2d83dae3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Armor</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=19bc2fde31ea0812</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>Sr. QE (Senior Quality Engineer, APIs)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, Azure, DynamoDB, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=c4837acc95c44131</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Sr. QE (Senior Quality Engineer, APIs)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, Azure, DynamoDB, ELT, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=5641d051b78dc3e5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Senior Software Engineer - Python - AI Platform</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>HEB</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>RDS, GCP, Vertex AI, Scala, Kafka, Data Modeling, CI/CD, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=a91ebd3753be4d7e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, HDFS, Hive, MapReduce, YARN, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2360e7b180f47f44</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8a8409fe728e8a</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Health Data Analytics Institute</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Dedham, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, IAM, Azure, GCP, Scala, CI/CD</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8386249f9122b7d3</t>
+          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Armor</t>
+          <t>Lancer Worldwide</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,437 +3636,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Scala, Data Modeling, ELT, Power BI, CI/CD, Python</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19bc2fde31ea0812</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Python - AI Platform</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>HEB</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>RDS, GCP, Vertex AI, Scala, Kafka, Data Modeling, CI/CD, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a91ebd3753be4d7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Evanston, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Waitsfield, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>IT Developer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>First Horizon Bank</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6524e8d17d74caa</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2a1044948ee5eed</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Engineer II</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f0406c507a72f7b8</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Engineer II- .Net</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Splunk, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5f9a72c26d6c4f36</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Architect AI ML</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>3Pillar Global</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Nightingale College</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Platform Architect - FinOps experience is Mandatory</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>VTekis Consulting LLP</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Plainsboro, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, ETL, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6ad43b99cd7044e9</t>
+          <t>https://www.indeed.com/viewjob?jk=700578b94883b043</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,42 +1186,42 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>DevOps Engineer - US</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>micro1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,42 +1301,42 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
@@ -1413,52 +1413,52 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Start Tek Pro</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, S3, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=9f5fc1df6a4b1ab2</t>
         </is>
       </c>
     </row>
@@ -1588,17 +1588,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
@@ -1756,14 +1756,14 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Wilson Elser</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Python Full Stack Developer with Agentic AI</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>System Edge LLC.</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, GitHub Actions, Docker, Kubernetes</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c635fc8d326af21</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f35dd0ad91911ba0</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Gen AI Platform &amp; Deployment Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>GeoStabilization International</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=358142c776463567</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (AWS, FiveTran, dbt, Snowflake)</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BOK Financial</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8b6b881616069c2</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Summer Intern - Data Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Dataflow, Hadoop, Spark, Data Modeling</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5a9e990dda6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,67 +2561,67 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2696,29 +2696,29 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,67 +2806,67 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Backend Architect - Device Management Platforms</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Elevance Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=143762682a9d9c04</t>
+          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,14 +2911,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Snowflake Developer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,15 +2928,15 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Waitsfield, VT, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>IT Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>First Horizon Bank</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Nightingale College</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Backend Engineer - MoneyLion</t>
+          <t>Architect AI ML</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Gen Digital Inc.</t>
+          <t>3Pillar Global</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, SQS, API Gateway, Scala, Kafka, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5243fde3ff4e011</t>
+          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Clinical Data Scientist, Human Capital</t>
+          <t>IS Technical Specialist</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CHS Corporate</t>
+          <t>Huntington Bank</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,402 +3251,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Oracle, Power BI, Tableau, Python, SQL</t>
+          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bfe6028a2d83dae3</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Armor</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19bc2fde31ea0812</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Sr. QE (Senior Quality Engineer, APIs)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Subway</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Shelton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, Azure, DynamoDB, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4837acc95c44131</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Sr. QE (Senior Quality Engineer, APIs)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Subway</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Shelton, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, Azure, DynamoDB, ELT, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5641d051b78dc3e5</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Python - AI Platform</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>HEB</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>RDS, GCP, Vertex AI, Scala, Kafka, Data Modeling, CI/CD, Terraform, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-04-21</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a91ebd3753be4d7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Evanston, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Architect AI ML</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>3Pillar Global</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Waitsfield, VT, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>IT Developer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>First Horizon Bank</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>IS Technical Specialist</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Huntington Bank</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Nightingale College</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Salt Lake City, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Analyst</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Lancer Worldwide</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Scala, Data Modeling, ELT, Power BI, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=700578b94883b043</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,35 +468,35 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Azure Data Engineer with Power BI and C# .NET exp--Need Government domain</t>
+          <t>Bid Role - Data Architect (STAR 4275)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Infopeople Corporation</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Queens, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Hadoop, Hive, Spark, PySpark</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07efb549ef55e02</t>
+          <t>https://www.indeed.com/viewjob?jk=1801c08f952fa8a2</t>
         </is>
       </c>
     </row>
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, SQL Server, PostgreSQL, MongoDB, NoSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,67 +601,67 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11348aaa79db186f</t>
+          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Engineer/Sr Engineer, IT Data</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Swire Coca-Cola</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Engineer - AI &amp; Data Management</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,42 +871,42 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,129 +916,129 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=e70923864f640df6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,104 +1046,104 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,102 +1231,102 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>DevOps Engineer - US</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>micro1</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, GCP, Scala</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77ce756f28346f96</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps &amp; MLOps Engineer</t>
+          <t>Data Platform Engineer- 6 Month Assignment</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TailoredSearch</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, Azure, GCP, BigQuery, NoSQL, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,137 +1406,137 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9675df96a6994487</t>
+          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>ETL Tester</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>V-ENVISAGE SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Start Tek Pro</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f5fc1df6a4b1ab2</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,59 +1581,59 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=8df970db5b7b3a83</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Wilson Elser</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Scala, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64b9306d8fcf8bad</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,112 +2026,112 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,94 +2176,94 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Quality Assurance Analyst / ETL Tester</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>DATAMAXIS</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,102 +2561,102 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,172 +2771,172 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,172 +3016,172 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Waitsfield, VT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+          <t>AWS, Azure, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=cdf78475cc5cb677</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Nightingale College</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Snowflake, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, pytest</t>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65756ab49eefec88</t>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Architect AI ML</t>
+          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>3Pillar Global</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Basking Ridge, NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2d6b6112e0fb25e</t>
+          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>IS Technical Specialist</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Huntington Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Git, Python</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,497 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=692fdccdd13ebb3b</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Data Warehouse</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Amplitude</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Snowflake Developer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Herndon, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - GM Motorsports</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Waitsfield, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>IT Developer</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>First Horizon Bank</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Evanston, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ac2326d031282c1e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,17 +783,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>AWS Data Engineer with Databricks Exp.</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,172 +986,172 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70923864f640df6</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
@@ -1173,160 +1173,160 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Software Development in Test (SDET III)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
+          <t>https://www.indeed.com/viewjob?jk=f788c85d6ae79fd9</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=e70923864f640df6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,522 +1336,522 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer- 6 Month Assignment</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Medallion Architecture, Cloud Storage, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ed470f2bb02fca0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ETL Tester</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>V-ENVISAGE SOLUTIONS INC</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, ETL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4cc527ce35e5f595</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>15.3</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df970db5b7b3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,67 +1966,67 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Senior Software Engineer, Data Ingestion Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Block</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco Bay Area, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,124 +2176,124 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>Software Engineer - SRE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DATAMAXIS</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d7a677f4736a542</t>
+          <t>https://www.indeed.com/viewjob?jk=8df970db5b7b3a83</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2302,116 +2302,116 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,67 +2421,67 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Modeling Engineer/Architect - Onsite/Hybrid</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea6deb35ddeb25ec</t>
+          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Miron Construction Co., Inc.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Neenah, WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,137 +2491,137 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,207 +2631,207 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Java Developer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Machine learning Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Pennington, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,137 +3016,137 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c01a1373d407b3e6</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf78475cc5cb677</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Voya Financial</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,137 +3156,137 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=dea0d4b03bd0e250</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>EDW Quality Engineer (QA / Data Warehouse Tester)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fluke</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Basking Ridge, NJ, US USA</t>
+          <t>Everett, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Snowflake, Snowflake Schema, Dimension Tables, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fc92b881a9200b86</t>
+          <t>https://www.indeed.com/viewjob?jk=de9989cbbb09da95</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,67 +3296,67 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37079c463898c2dd</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,102 +3401,102 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. Cloud Engineer - SAP Platforms</t>
+          <t>Data scientist</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Herndon, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67340d847b0f971b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,102 +3541,102 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Waitsfield, VT, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,110 +3646,775 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IT Developer</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>First Horizon Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Azure DevOps, Docker, Kubernetes, AKS, pytest, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7533d2e71665596c</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>Machine Learning Threat Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cdf78475cc5cb677</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Software Development Engineer III</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Wipro</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Redmond, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Software Engineer, Identity and Access Management</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Fitch Group</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, API Gateway, IAM, Oracle, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd39762b7995bcd8</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Sunrise, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Dun &amp; Bradstreet</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Data Warehouse</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Amplitude</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Snowflake Developer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Data Modeling, ELT, Splunk, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b34891601e8f94ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - GM Motorsports</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40951da6c2d8f0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Waitsfield, VT, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Evanston, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
           <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
         </is>
       </c>
-      <c r="B95" t="inlineStr">
+      <c r="B114" t="inlineStr">
         <is>
           <t>General Motors (GM)</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D95" t="n">
+      <c r="D114" t="n">
         <v>10.4</v>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ac2326d031282c1e</t>
         </is>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G114"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Bid Role - Data Architect (STAR 4275)</t>
+          <t>Senior Software Engineer – Python / PySpark (Mainframe Modernization) (contract)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Leading Path Consulting</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, Azure, Databricks, Hadoop, HDFS, Hive</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,59 +496,59 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1801c08f952fa8a2</t>
+          <t>https://www.indeed.com/viewjob?jk=015fe1a494f266bf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL, Python, Cloud)</t>
+          <t>Bid Role - Data Architect (STAR 4275)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>Leading Path Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=1801c08f952fa8a2</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Data Engineer (SQL, Python, Cloud)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,102 +566,102 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34bd7ad3cc55cc</t>
+          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
+          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34bd7ad3cc55cc</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Data</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Spark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75e15a03b23795b5</t>
+          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d629ec9761b3e8f</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Swire Coca-Cola</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, Scala, Snowflake, SQL Server, Kimball</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17a926a902e4ab1a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5d16b369ad8f0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AWS Data Engineer with Databricks Exp.</t>
+          <t>Software Engineer I</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0c0bcd9b11d0c54</t>
+          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,19 +986,19 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
+          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Credera</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, SQS, SNS, ECS, RDS</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0a8e6675d7ad8e4</t>
+          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2859c21fcc6b9b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development in Test (SDET III)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>LVT (LiveView Technologies)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>American Fork, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e65ae12c9231691</t>
+          <t>https://www.indeed.com/viewjob?jk=f788c85d6ae79fd9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Threat Intelligence Automation Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, Glue, Lambda, SQS, RDS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=deb9ad8464ceb6e6</t>
+          <t>https://www.indeed.com/viewjob?jk=e70923864f640df6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Credera</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,134 +1186,134 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Hadoop, Oozie, Spark, Scala, Kafka, SQL Server</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0faede29102fb7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Development in Test (SDET III)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f788c85d6ae79fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70923864f640df6</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,77 +1441,77 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Harley-Davidson, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Data Engineer Senior</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>The University of Michigan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,104 +1781,104 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Management Architect (Manufacturing)</t>
+          <t>Software Development, Cloud Architecture, IT Support &amp; Data Analytics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>E Logic</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, NoSQL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=61f7a9c234166321</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,42 +1921,42 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>AI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=08d6323e8d4d4853</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Ingestion Platform</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco Bay Area, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Kafka Connect, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0797708a811c3517</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,17 +2166,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer - SRE</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8df970db5b7b3a83</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Miron Construction Co., Inc.</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Neenah, WI, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5feb851e71d2137</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,77 +2761,77 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java Developer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, NoSQL, Splunk, CI/CD, Jenkins, Maven</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3618c6745c7b69</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Machine learning Engineer</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pennington, NJ, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=069d340f07134822</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
@@ -2918,17 +2918,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Senior Cloud Security Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Acrisure LLC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=dea0d4b03bd0e250</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Fluke</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Everett, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=de9989cbbb09da95</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Voya Financial</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33104d171736f045</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76df256873f2c893</t>
+          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Joliet, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea0d4b03bd0e250</t>
+          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Everett, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9989cbbb09da95</t>
+          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,192 +3321,192 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Data Engineer with AI Engineering</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data scientist</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bfed15cc40a8e20</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>Software Engineer, Identity and Access Management</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, Lambda, API Gateway, IAM, Oracle, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=fd39762b7995bcd8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Kafka, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdf78475cc5cb677</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer II, Data Warehouse</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Amplitude</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Hive, Spark, PySpark, Kafka, Snowflake, Data Modeling, ELT, DataOps, CI/CD, Airflow</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,59 +3856,59 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7caec4c69e7fec</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer, Identity and Access Management</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Oracle, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd39762b7995bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Barrington, RI, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=5e8028d0d5b1df65</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Caldwell, ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=a5cdda50be7be595</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Marion, IA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=c871627a5fbd7d46</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Birmingham, AL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,34 +4021,34 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
+          <t>https://www.indeed.com/viewjob?jk=129e7c3974efc5f3</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>PySpark Software Engineer III - Python/Java/SQL</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Newmarket, NH, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,34 +4056,34 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e62bf7828019acf</t>
+          <t>https://www.indeed.com/viewjob?jk=ed8aea93c76f0472</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Snowflake Developer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Azure, Synapse Analytics, Databricks, Hadoop, HDFS, Hive, YARN, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3378351c12aad9f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7559827bdb57a0fb</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Frankfort, KY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Snowflake, dbt, CI/CD, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8074af46a35d5ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=74277bcbbe107636</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Full Stack Software Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, IAM, Data Modeling, ELT, Splunk, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b34891601e8f94ce</t>
+          <t>https://www.indeed.com/viewjob?jk=12cae2ae25e8b014</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Rehoboth Beach, DE, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+          <t>https://www.indeed.com/viewjob?jk=6306faf8c94f493a</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Liberty, MO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+          <t>https://www.indeed.com/viewjob?jk=6e0abbf2db2329d7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40951da6c2d8f0ad</t>
+          <t>https://www.indeed.com/viewjob?jk=fddf6b2cd77b36d0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+          <t>https://www.indeed.com/viewjob?jk=6232b3c854695d12</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Agri-Mark, Inc. / Cabot Creamery</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Waitsfield, VT, US USA</t>
+          <t>Portland, ME, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, SQL Server, ETL, ELT, dbt, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb12ce4b2932b6b</t>
+          <t>https://www.indeed.com/viewjob?jk=2acdbfef72fe8382</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Tulsa, OK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,34 +4371,34 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+          <t>https://www.indeed.com/viewjob?jk=667feb24362ea298</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
+          <t>SDET- Payments &amp; Telehealth</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ensora Health</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fargo, ND, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,15 +4406,1310 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dd95cb5f129ba4a3</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Provo, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27fe3748b4c6e9ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Harrisburg, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=96e55f69edf8e710</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Newport, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f877d29517d1e8c</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Hudson, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=578051612c793f74</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Annapolis, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a2a751d1b4654154</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=720d2d19c637dbd7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7d3ec8a3acdaf608</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bcde40daa1b5a67</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Las Vegas, NV, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b19225c5d43f5354</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9eda53066f047cc</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Omaha, NE, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d2b852deb59b35a</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Dayton, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ebd8c576a7f84b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Richland, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c43ffb9dc8728db</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Derby, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0deee98ca536f71b</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48cbf9152cf68ba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Monrovia, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c245b04f72dbcaf</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Clinton, MS, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3c0ae7ba24ecce9d</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Watson, AR, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=937b2de1fa924199</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fb756925d51a6b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Tyler, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=589226c2de6af70c</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Boulder, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1721b2eddbb95215</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Stafford, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85f8c3b8c340ef19</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Overland Park, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e411377c0061c4f</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=193365b70ef7abc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Missoula, MT, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fb5e93fe4c3b2ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Parlin, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b8a979d87a9e8d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Albuquerque, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8adc97440a91f562</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Medway, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5260f1234c40edbb</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f2191c8bc4701830</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>SDET- Payments &amp; Telehealth</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Ensora Health</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Pierre, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c6b9c845547786b</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Eli Lilly</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Data Modeling, ELT, Splunk, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b34891601e8f94ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - GM Motorsports</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=40951da6c2d8f0ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Evanston, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
           <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F151" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="G151" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=ac2326d031282c1e</t>
         </is>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,60 +538,60 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer (SQL, Python, Cloud)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AEM Corporation</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Dataflow, Spark, Scala, Kafka, NoSQL, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
+          <t>https://www.indeed.com/viewjob?jk=49b6a92728349bc5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Select Minds LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, Databricks, Spark</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
+          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical Architect-Datawarehousing</t>
+          <t>Data Engineer (SQL, Python, Cloud)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>AEM Corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,119 +636,119 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe34bd7ad3cc55cc</t>
+          <t>https://www.indeed.com/viewjob?jk=eb194f6feb01a9b5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
+          <t>https://www.indeed.com/viewjob?jk=10720f22d9d38621</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Cloud Network Automation Engineer</t>
+          <t>Technical Architect-Datawarehousing</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Marlborough, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, S3, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
+          <t>https://www.indeed.com/viewjob?jk=fe34bd7ad3cc55cc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>AV Safety Engineering Analytics AI/ML Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tradeweb</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Spark, PySpark</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
+          <t>https://www.indeed.com/viewjob?jk=675259892fa0b51c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GenAI Threat Intelligence Analyst</t>
+          <t>Cloud Network Automation Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -762,11 +762,11 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
+          <t>https://www.indeed.com/viewjob?jk=0a0cf6116e02d635</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Applied Technology Services</t>
+          <t>Tradeweb</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Adelphi, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
+          <t>AWS, Redshift, S3, IAM, RDS, GCP, Spark, Kafka, Dask, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb2021c38a5314d9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GenAI Threat Intelligence Analyst</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, SNS, ECS, IAM, Databricks, Delta Live Tables</t>
+          <t>AWS, RDS, Azure, Databricks, Blob Storage, Google Cloud Platform, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5512aba12eaa248e</t>
+          <t>https://www.indeed.com/viewjob?jk=5efecdb56da9cdd1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Databricks Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metropolitan Commercial Bank</t>
+          <t>Applied Technology Services</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Adelphi, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
+          <t>AWS, S3, Azure, Databricks, Data Lake Storage, Unity Catalog, Medallion Architecture, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
+          <t>https://www.indeed.com/viewjob?jk=88d5142fe158dffb</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Select Minds LLC</t>
+          <t>Metropolitan Commercial Bank</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, IAM</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Spark, PySpark, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9d0ac6d3cf445a9</t>
+          <t>https://www.indeed.com/viewjob?jk=25250927f01c87fd</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development in Test (SDET III)</t>
+          <t>Applications Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LVT (LiveView Technologies)</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>American Fork, UT, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,104 +1116,104 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, MongoDB, DynamoDB, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f788c85d6ae79fd9</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Threat Intelligence Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, SQS, RDS, Azure, Scala, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e70923864f640df6</t>
+          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Applications Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>TeraWatt Infrastructure</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4c524177840a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer, Full Stack - AI (Chicago)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b7e79accc7c2528</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TeraWatt Infrastructure</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cf13a405f291139</t>
+          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineer, Full Stack - AI (Chicago)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bb35a3533f1ee6</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineering &amp; Quality - Software Engineer, Full Stack - AI</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,104 +1326,104 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, Azure, Blob Storage, Spark, PySpark, Kafka, Snowflake</t>
+          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf6b928dd59e0c41</t>
+          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b54324d4bccebe</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, Azure, GCP, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45cec5906abac43f</t>
+          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Metropolis</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc4628968aad9e2</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0eb5fc1d601c0028</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Metropolis</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, SNS, RDS, Spark, PySpark, Scala, Snowflake, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acae1b7fc51e9a39</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,59 +1641,59 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior ML/GenAI Ops Engineer - Milwaukee, WI</t>
+          <t>Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Harley-Davidson, Inc.</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, dbt, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8a0e12a78fd06e23</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1703,50 +1703,50 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,102 +1756,102 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer Senior</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The University of Michigan</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb7fb4fe859681f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Management Architect (Manufacturing)</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,67 +1861,67 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Development, Cloud Architecture, IT Support &amp; Data Analytics</t>
+          <t>AI Engineer / Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>E Logic</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, PostgreSQL, NoSQL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2025-07-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61f7a9c234166321</t>
+          <t>https://www.indeed.com/viewjob?jk=08d6323e8d4d4853</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>Senior Engineer - Agentic AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Developer - Used Car Marketplace</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Distinguished Engineer -</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allstate Insurance</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, GCP, Snowflake, ELT, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=087eb595cff7bd93</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Fidelity TalentSource</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Smithfield, RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,182 +2061,182 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Azure, GCP, Hadoop, Hive, HBase, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3d1d7dfa9557f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AI Engineer / Data Scientist</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d6323e8d4d4853</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer/SRE - GM Energy</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0413ce8de5fcca6a</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Engineer - Agentic AI</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5daf8f72a4fd9ab6</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Fidelity TalentSource</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Smithfield, RI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Spark, Scala, Snowflake, Oracle, ETL, Jenkins, Maven</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cc22367a2ce3d9f</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Developer - Used Car Marketplace</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d487bcb34632271a</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Kharon</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Gerber Childrenswear, Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Greenville, SC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,102 +2666,102 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Software Engineer - Intermediate</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Cloud Security Engineer</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Acrisure LLC</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,67 +3051,67 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dea0d4b03bd0e250</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Fluke</t>
+          <t>Funding Force Ai</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Everett, WA, US USA</t>
+          <t>Astoria, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, IAM, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de9989cbbb09da95</t>
+          <t>https://www.indeed.com/viewjob?jk=165552b234d04969</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,137 +3121,137 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54994fef84e9e218</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Joliet, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7b23a51a16ead4c</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8838a726bcf4f615</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps Engineer — Data &amp; AI Platforms - AIRLKLHV</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MLOps, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ade083334b9a870</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3278,32 +3278,32 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3313,42 +3313,42 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,49 +3436,49 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer with AI Engineering</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Snowflake, NoSQL, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38c1b47e8e6f1fa</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,85 +3488,85 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,84 +3646,84 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Information Technology - Data Integration Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Magnolia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Waco, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer, Identity and Access Management</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Evanston, IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Oracle, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd39762b7995bcd8</t>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>Senior Software Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II, Data Warehouse</t>
+          <t>Senior Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Amplitude</t>
+          <t>Douglas Machine Inc.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Alexandria, MN, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,1907 +3811,17 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>S3, RDS, Azure, Databricks, Blob Storage, Kafka, Snowflake, DynamoDB, ETL, ELT</t>
+          <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97f7bc28ece22e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>American Express</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Sunrise, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Barrington, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5e8028d0d5b1df65</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Caldwell, ID, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5cdda50be7be595</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Marion, IA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c871627a5fbd7d46</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Birmingham, AL, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=129e7c3974efc5f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Newmarket, NH, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed8aea93c76f0472</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7559827bdb57a0fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Frankfort, KY, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=74277bcbbe107636</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=12cae2ae25e8b014</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Rehoboth Beach, DE, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6306faf8c94f493a</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Liberty, MO, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e0abbf2db2329d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Greenville, SC, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fddf6b2cd77b36d0</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Nashville, TN, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6232b3c854695d12</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Portland, ME, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2acdbfef72fe8382</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Tulsa, OK, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=667feb24362ea298</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Fargo, ND, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dd95cb5f129ba4a3</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Provo, UT, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27fe3748b4c6e9ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Harrisburg, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96e55f69edf8e710</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Newport, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7f877d29517d1e8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Hudson, WI, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=578051612c793f74</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Annapolis, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a751d1b4654154</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=720d2d19c637dbd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Baton Rouge, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7d3ec8a3acdaf608</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bcde40daa1b5a67</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Las Vegas, NV, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b19225c5d43f5354</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9eda53066f047cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Omaha, NE, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1d2b852deb59b35a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Dayton, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8ebd8c576a7f84b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Richland, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c43ffb9dc8728db</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Derby, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0deee98ca536f71b</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=48cbf9152cf68ba9</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Monrovia, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5c245b04f72dbcaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Clinton, MS, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3c0ae7ba24ecce9d</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Watson, AR, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=937b2de1fa924199</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fb756925d51a6b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Tyler, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=589226c2de6af70c</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Boulder, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1721b2eddbb95215</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Stafford, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85f8c3b8c340ef19</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e411377c0061c4f</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=193365b70ef7abc6</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Missoula, MT, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fb5e93fe4c3b2ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Parlin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8a979d87a9e8d2</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Albuquerque, NM, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8adc97440a91f562</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Medway, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5260f1234c40edbb</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f2191c8bc4701830</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>SDET- Payments &amp; Telehealth</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Ensora Health</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Pierre, SD, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6c6b9c845547786b</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Eli Lilly</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Data Modeling, ELT, Splunk, CI/CD, Docker, Kubernetes, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b34891601e8f94ce</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>SEI Investments</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Oaks, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Concord, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Information Technology - Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Magnolia</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40951da6c2d8f0ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Information Technology - Data Integration Engineer</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Magnolia</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Waco, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Software Engineer II</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>RELX Group</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Evanston, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-04-20</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>AV Safety Engineering Analytics Engineer (GPSSC)</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>General Motors (GM)</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ac2326d031282c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-30.xlsx
+++ b/results/job_matches_2026-04-30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JUUL Labs</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
+          <t>AWS, S3, ECS, IAM, RDS, GCP, Dataflow, Cloud Storage, Scala, Splunk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
+          <t>https://www.indeed.com/viewjob?jk=c63edb85327f9aef</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DEVELOPER L3(CONTRACT)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
+          <t>AWS, RDS, GCP, BigQuery, Vertex AI, Scala, Snowflake, SQL Server, MySQL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
+          <t>https://www.indeed.com/viewjob?jk=de10d304d09880c3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>DEVELOPER L3(CONTRACT)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Databricks, Cloud Storage, Spark, PySpark, Scala, Snowflake, Time Travel, Databricks Lakehouse, Snowflake Schema</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1c37881d8861b3d6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
+          <t>https://www.indeed.com/viewjob?jk=fb97e11dedc46f7e</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Ad Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
+          <t>AWS, Azure, Databricks, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
+          <t>https://www.indeed.com/viewjob?jk=fb853658114af880</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Engineer Senior</t>
+          <t>Senior Ad Ops Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Texas Capital Bank</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=3d412becc7b99de0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Management Architect (Manufacturing)</t>
+          <t>Platform Engineer Senior</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Infor</t>
+          <t>Texas Capital Bank</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Snowflake, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
+          <t>https://www.indeed.com/viewjob?jk=09ac756571edd2b5</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>OnStar Vehicle Data System Engineer</t>
+          <t>Data Management Architect (Manufacturing)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Infor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
+          <t>AWS, RDS, Azure, Hadoop, Spark, Scala, Oracle, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
+          <t>https://www.indeed.com/viewjob?jk=e45199011cbe2990</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
+          <t>OnStar Vehicle Data System Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Esri</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Redlands, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,42 +1746,42 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Sqoop, Scala, Kafka, Oracle, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
+          <t>https://www.indeed.com/viewjob?jk=23b443a7cc921497</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Software Engineer I – AI Assistant Framework, ArcGIS Enterprise</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Esri</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Redlands, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2546eaf4a3e50baf</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Intelligent Medical Objects</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
+          <t>AWS, Redshift, Athena, S3, IAM, Hadoop, Spark, Kafka, Snowflake, Splunk</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
+          <t>https://www.indeed.com/viewjob?jk=0f01d239e5c828f6</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Infrastructure-as-Code (IaC) Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Intelligent Medical Objects</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Spark, Scala, Data Modeling, dbt, Power BI</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
+          <t>https://www.indeed.com/viewjob?jk=c4869d3a6ac24136</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Engineer / Data Scientist</t>
+          <t>Infrastructure-as-Code (IaC) Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d6323e8d4d4853</t>
+          <t>https://www.indeed.com/viewjob?jk=ca35900639cbe443</t>
         </is>
       </c>
     </row>
@@ -2078,130 +2078,130 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Commercial Software</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
+          <t>https://www.indeed.com/viewjob?jk=79a2a043dc5cdb8f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Brooklyn, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
+          <t>https://www.indeed.com/viewjob?jk=e387db2c2b866baa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LexisNexis Legal &amp; Professional</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Buffalo, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
+          <t>https://www.indeed.com/viewjob?jk=18a022cbc2b4d934</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Machine Learning Threat Intelligence Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,59 +2211,59 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
+          <t>https://www.indeed.com/viewjob?jk=5cc4f959dd712f8a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Java Database Developer - JDBDEV 0430 HS#02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Evolus</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Newport Beach, CA, US USA</t>
+          <t>Yonkers, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
+          <t>https://www.indeed.com/viewjob?jk=688d7763683eecad</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Commercial Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Kharon</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Oracle, MySQL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7c790cc82896e043</t>
+          <t>https://www.indeed.com/viewjob?jk=4ca1245fe1b2a956</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer II</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
+          <t>https://www.indeed.com/viewjob?jk=35085eed81ec8943</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. DevOps Engineer</t>
+          <t>Senior Machine Learning Engineer III ***Raleigh, NC***</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Eclypsium</t>
+          <t>LexisNexis Legal &amp; Professional</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, SQS, RDS, Hadoop, Spark, Scala, Kafka, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
+          <t>https://www.indeed.com/viewjob?jk=70897e01c57b5008</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Machine Learning Threat Intelligence Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
+          <t>https://www.indeed.com/viewjob?jk=36a73b40629cc484</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Evolus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Newport Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>Azure, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT, dbt, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
+          <t>https://www.indeed.com/viewjob?jk=caa4efd9c3316730</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Artificial Intelligence/Machine Learning Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Logic, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Kinesis, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, MLflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
+          <t>https://www.indeed.com/viewjob?jk=e34c2e31eeb33f9e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. API Engineer</t>
+          <t>Senior Site Reliability Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
+          <t>https://www.indeed.com/viewjob?jk=6fa53cf983e1a6d0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, APIs</t>
+          <t>Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Subway</t>
+          <t>Eclypsium</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Shelton, CT, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
+          <t>AWS, Lambda, RDS, Azure, Google Cloud Platform, GCP, Cloud Storage, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
+          <t>https://www.indeed.com/viewjob?jk=746eae080f33e9b0</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
+          <t>https://www.indeed.com/viewjob?jk=6b02c1c05cdd16b9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Gerber Childrenswear, Inc</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Greenville, SC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef46594bb4b76db</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9aa07e40090d93</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Remote)</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tallahassee, FL, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
+          <t>https://www.indeed.com/viewjob?jk=4277c27f2f782266</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Java Developers</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vibotek LLC</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,94 +2666,94 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
+          <t>https://www.indeed.com/viewjob?jk=ef0f69867247772a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer, APIs</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d448f5377465e81</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data and Analytics Platform Architect</t>
+          <t>Sr. API Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Motiva Enterprises LLC</t>
+          <t>Subway</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Shelton, CT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
+          <t>AWS, Lambda, SQS, SNS, API Gateway, RDS, Azure, Scala, DynamoDB, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
+          <t>https://www.indeed.com/viewjob?jk=aca94a7c92083f9d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Machine Learning Engineer (Remote)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Mayo Clinic</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rochester, MN, US USA</t>
+          <t>Tallahassee, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Vertex AI, Scala, NoSQL, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
+          <t>https://www.indeed.com/viewjob?jk=fdbdb16275078800</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Software Engineer - Intermediate</t>
+          <t>Sr. Java Developers</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Vibotek LLC</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Dataflow, Scala, SQL Server, MySQL, CI/CD, Maven</t>
+          <t>AWS, HBase, Spark, Scala, Kafka, Oracle, Cassandra, NoSQL, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad45ab734c8ec6fe</t>
+          <t>https://www.indeed.com/viewjob?jk=061d80fcb09266da</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Hadoop, Hive, Spark, PySpark, Scala, Oracle, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
+          <t>https://www.indeed.com/viewjob?jk=8629753fa2cdcb2f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Full Stack, Data &amp; Analytics Engineer</t>
+          <t>Data and Analytics Platform Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Motiva Enterprises LLC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, Medallion Architecture, Spark, Scala, Snowflake, Data Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
+          <t>https://www.indeed.com/viewjob?jk=45b3fd0f3632a8d6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Associate Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Mayo Clinic</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Allen Park, MI, US USA</t>
+          <t>Rochester, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, ELT, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
+          <t>https://www.indeed.com/viewjob?jk=8081ee3f40d7d31c</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tennessee Titans</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
+          <t>https://www.indeed.com/viewjob?jk=57b0af5961338ef2</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
+          <t>Full Stack, Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Snowflake, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
+          <t>https://www.indeed.com/viewjob?jk=6b0db4093988ff3c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Reliability Engineer (Autonomous Vehicles)</t>
+          <t>Software Development Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Allen Park, MI, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
+          <t>https://www.indeed.com/viewjob?jk=9607f88f3f9962f3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AI/ML Developer II (Remote)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>The Home Depot</t>
+          <t>Tennessee Titans</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Snowflake, Data Modeling, ELT, dbt</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,102 +3051,102 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
+          <t>https://www.indeed.com/viewjob?jk=b7b90aa43b4806b0</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Systems Engineer, Release Reliability &amp; Automation (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Funding Force Ai</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Astoria, NY, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=165552b234d04969</t>
+          <t>https://www.indeed.com/viewjob?jk=f97782145b5d3f94</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Quality Automation Engineer (SDET) - Career</t>
+          <t>Reliability Engineer (Autonomous Vehicles)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
+          <t>https://www.indeed.com/viewjob?jk=cf25e4c14df46394</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
+          <t>AI/ML Developer II (Remote)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>The Home Depot</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, NoSQL, ETL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
+          <t>https://www.indeed.com/viewjob?jk=fb663396a5bc1b79</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Quality Automation Engineer (SDET) - Career</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Cityblock Health</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Dataflow, Scala, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
+          <t>https://www.indeed.com/viewjob?jk=b597edf918184e10</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Infrastructure &amp; Security Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Carrier</t>
+          <t>HerculesAI</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Campbell, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, IAM, Azure, GCP, Splunk, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
+          <t>https://www.indeed.com/viewjob?jk=997e47a23e0d8261</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Platform Engineer</t>
+          <t>Software Engineer III - Data, AWS, ETL, Java/Python,</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>buzz solutions</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, ETL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
+          <t>https://www.indeed.com/viewjob?jk=24b2eb0df8c7e284</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - GM Motorsports</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Cityblock Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
+          <t>AWS, IAM, RDS, Azure, GCP, BigQuery, PostgreSQL, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
+          <t>https://www.indeed.com/viewjob?jk=76d763c610ac1510</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer- GM Energy</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Carrier</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
+          <t>AWS, RDS, Azure, Medallion Architecture, GCP, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,19 +3331,19 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
+          <t>https://www.indeed.com/viewjob?jk=ab7c6d265d3522d2</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Platform Architect (Snowflake)</t>
+          <t>Applied Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Coastal</t>
+          <t>buzz solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
+          <t>AWS, GCP, Scala, DynamoDB, MLOps, MLflow, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7453cbf812ce3c18</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Data Engineer - GM Motorsports</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Concord, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Scala, Kafka, Databricks Lakehouse, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
+          <t>https://www.indeed.com/viewjob?jk=c80625f8482f70fb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Wipro</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Redmond, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,42 +3426,42 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
+          <t>https://www.indeed.com/viewjob?jk=83fb65ae6e18206f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer III – Python/PySpark/AWS</t>
+          <t>Senior Backend Software Engineer- GM Energy</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, GCP, Scala, Kafka, Snowflake, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
+          <t>https://www.indeed.com/viewjob?jk=51fb08298ca2e944</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
+          <t>Data Platform Architect (Snowflake)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Coastal</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3492,108 +3492,108 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, Snowflake, Data Modeling, Kimball, ETL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
+          <t>https://www.indeed.com/viewjob?jk=58854506afe876e4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
+          <t>https://www.indeed.com/viewjob?jk=1f950bd314b17c8f</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PySpark Data Engineer III - Python/Java/SQL</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Wipro</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Redmond, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
+          <t>https://www.indeed.com/viewjob?jk=93121f9bd0f39c05</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
+          <t>Software Engineer III – Python/PySpark/AWS</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Databricks, Hadoop, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
+          <t>https://www.indeed.com/viewjob?jk=991d5ceb2074b137</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer (R-19149)</t>
+          <t>AV Safety Engineering Analytics Simulation Engineer (GPSSC)</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Dun &amp; Bradstreet</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Tableau, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
+          <t>https://www.indeed.com/viewjob?jk=759f2d176cc08b7e</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Information Technology - Data Integration Engineer</t>
+          <t>Software Engineer II, Global Servicing Technology</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Magnolia</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Waco, TX, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Kafka, Oracle, PostgreSQL, MongoDB, NoSQL, ETL, Git</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+          <t>https://www.indeed.com/viewjob?jk=f4bf42c50ee97107</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>PySpark Data Engineer III - Python/Java/SQL</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Evanston, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,24 +3706,24 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Data Modeling, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+          <t>https://www.indeed.com/viewjob?jk=926547138e49a51b</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - GM Motorsports</t>
+          <t>Senior Software Engineer – Cloud Engineering &amp; FinOps</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Concord, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+          <t>https://www.indeed.com/viewjob?jk=d576082b1c56db5c</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Platform Engineer (R-19149)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>Dun &amp; Bradstreet</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+          <t>https://www.indeed.com/viewjob?jk=cb41c4b9d93e0f98</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Business Intelligence Developer</t>
+          <t>Senior Full Stack Engineer - .NET (HYBRID)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Douglas Machine Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Alexandria, MN, US USA</t>
+          <t>Smyrna, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,15 +3811,295 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef040d1b01903853</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=229f6840535c3531</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=606324c85c044a5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Full‑Stack Developer (Java, React, Microservices) *Hybrid*</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Data Modeling, CI/CD, Azure DevOps, Docker</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f298bb4ddf8e9a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Information Technology - Data Integration Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Magnolia</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Waco, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=22a077ceb692752f</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>RELX Group</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Evanston, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3493170e435cd93</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - GM Motorsports</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>General Motors (GM)</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Concord, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, GCP, Scala, Kafka, MongoDB, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f660072154c9a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SEI Investments</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Oaks, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Kafka, Snowflake, Oracle, SQL Server, MySQL, MongoDB, Jenkins, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76c94610856b0496</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Senior Business Intelligence Developer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Douglas Machine Inc.</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Alexandria, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
           <t>RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, Dimensional Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f9d5d216fe71b48e</t>
         </is>
